--- a/artfynd/A 12801-2026 artfynd.xlsx
+++ b/artfynd/A 12801-2026 artfynd.xlsx
@@ -1202,7 +1202,7 @@
         <v>136392957</v>
       </c>
       <c r="B7" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 12801-2026 artfynd.xlsx
+++ b/artfynd/A 12801-2026 artfynd.xlsx
@@ -1202,7 +1202,7 @@
         <v>136392957</v>
       </c>
       <c r="B7" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 12801-2026 artfynd.xlsx
+++ b/artfynd/A 12801-2026 artfynd.xlsx
@@ -998,7 +998,7 @@
         <v>136394432</v>
       </c>
       <c r="B5" t="n">
-        <v>80590</v>
+        <v>80592</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1100,7 +1100,7 @@
         <v>136395269</v>
       </c>
       <c r="B6" t="n">
-        <v>80590</v>
+        <v>80592</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
         <v>136392957</v>
       </c>
       <c r="B7" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1508,7 +1508,7 @@
         <v>136393352</v>
       </c>
       <c r="B10" t="n">
-        <v>80589</v>
+        <v>80591</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         <v>136393389</v>
       </c>
       <c r="B11" t="n">
-        <v>80601</v>
+        <v>80603</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 12801-2026 artfynd.xlsx
+++ b/artfynd/A 12801-2026 artfynd.xlsx
@@ -1202,7 +1202,7 @@
         <v>136392957</v>
       </c>
       <c r="B7" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 12801-2026 artfynd.xlsx
+++ b/artfynd/A 12801-2026 artfynd.xlsx
@@ -998,7 +998,7 @@
         <v>136394432</v>
       </c>
       <c r="B5" t="n">
-        <v>80592</v>
+        <v>80596</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1100,7 +1100,7 @@
         <v>136395269</v>
       </c>
       <c r="B6" t="n">
-        <v>80592</v>
+        <v>80596</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
         <v>136392957</v>
       </c>
       <c r="B7" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1508,7 +1508,7 @@
         <v>136393352</v>
       </c>
       <c r="B10" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         <v>136393389</v>
       </c>
       <c r="B11" t="n">
-        <v>80603</v>
+        <v>80607</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 12801-2026 artfynd.xlsx
+++ b/artfynd/A 12801-2026 artfynd.xlsx
@@ -998,7 +998,7 @@
         <v>136394432</v>
       </c>
       <c r="B5" t="n">
-        <v>80596</v>
+        <v>80598</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1100,7 +1100,7 @@
         <v>136395269</v>
       </c>
       <c r="B6" t="n">
-        <v>80596</v>
+        <v>80598</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
         <v>136392957</v>
       </c>
       <c r="B7" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1508,7 +1508,7 @@
         <v>136393352</v>
       </c>
       <c r="B10" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         <v>136393389</v>
       </c>
       <c r="B11" t="n">
-        <v>80607</v>
+        <v>80609</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
